--- a/downloads/10.5281_zenodo.18940001/flehs4.xlsx
+++ b/downloads/10.5281_zenodo.18940001/flehs4.xlsx
@@ -817,7 +817,9 @@
         <v>41</v>
       </c>
       <c r="F2"/>
-      <c r="G2"/>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
